--- a/public/purify.xlsx
+++ b/public/purify.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:B6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -406,18 +406,6 @@
       <c r="B1" t="str">
         <v>Effect</v>
       </c>
-      <c r="C1" t="str">
-        <v>Effect Amt</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Effect Hits</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Effect Dur</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Effect Target</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -426,12 +414,6 @@
       <c r="B2" t="str">
         <v>burn</v>
       </c>
-      <c r="C2" t="str">
-        <v>1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -440,12 +422,6 @@
       <c r="B3" t="str">
         <v>thorns</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -454,9 +430,6 @@
       <c r="B4" t="str">
         <v>power combo</v>
       </c>
-      <c r="F4" t="str">
-        <v>Lightning</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -465,13 +438,18 @@
       <c r="B5" t="str">
         <v>float</v>
       </c>
-      <c r="F5" t="str">
-        <v>Fire</v>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Soul</v>
+      </c>
+      <c r="B6" t="str">
+        <v>powerful</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>